--- a/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
+++ b/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5609DEFE-0945-4AA8-8295-E5A81E31E5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161DD17-6581-49F3-B627-06A4CC600A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15630" yWindow="2925" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15630" yWindow="2925" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">batch1!$A$1:$K$241</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -486,6 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K241"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>40316</v>
       </c>
@@ -547,7 +547,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>40316</v>
       </c>
@@ -567,7 +567,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>40316</v>
       </c>
@@ -593,7 +593,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>40316</v>
       </c>
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>40316</v>
       </c>
@@ -645,7 +645,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>40316</v>
       </c>
@@ -671,7 +671,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>40316</v>
       </c>
@@ -697,7 +697,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>40316</v>
       </c>
@@ -723,7 +723,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>40316</v>
       </c>
@@ -749,7 +749,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>40316</v>
       </c>
@@ -775,7 +775,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>40316</v>
       </c>
@@ -798,7 +798,7 @@
         <v>71.95</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>40316</v>
       </c>
@@ -821,7 +821,7 @@
         <v>59.76</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>40411</v>
       </c>
@@ -841,7 +841,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>40411</v>
       </c>
@@ -861,7 +861,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>40411</v>
       </c>
@@ -887,7 +887,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>40411</v>
       </c>
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>40411</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>40411</v>
       </c>
@@ -965,7 +965,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>40411</v>
       </c>
@@ -991,7 +991,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>40411</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>40411</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>40411</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>40411</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>40411</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>40411</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>40411</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>40411</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>40411</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>40411</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>40411</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>40411</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>40411</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>40411</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>40411</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>40411</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>40411</v>
       </c>
@@ -1409,7 +1409,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>40416</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>40416</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>40416</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40416</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40416</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40416</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>40416</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>40416</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>40416</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>40416</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>40416</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>70.34</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>40416</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>78.77</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>40417</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>40417</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>12.305999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>40417</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>40417</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>40417</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>40417</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>40417</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>40417</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>40417</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>40417</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>40417</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>68.7</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>40417</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>65.69</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>40508</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>12.68</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>40508</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>40508</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>40508</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>40508</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>40508</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>40508</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>40508</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>40508</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>40508</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>40508</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>87.56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>40508</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>90.42</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>40614</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>40614</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>40614</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>40614</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>40614</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>40614</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>40614</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>40614</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>40614</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>40614</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>40614</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>40614</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>72.27</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>69.05</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>25</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>25</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>25</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>25</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>25</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>25</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>25</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>20</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>20</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>20</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>20</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>20</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>20</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>20</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>20</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>20</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>20</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>90.42</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>20</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>87.56</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>21</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>59.26</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>60.06</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>21</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>21</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>21</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>21</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>21</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>21</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>21</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>21</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>21</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>22</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>22</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>22</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>22</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>22</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>22</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>22</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>22</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>59.02</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>22</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>58.57</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>24</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>24</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>24</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>24</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>61.88</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>63.08</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>27</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>24.45</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>27</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>23.22</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>27</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>13.65</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>27</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>27</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>27</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>13.557</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>27</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>13.87</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>27</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>13.563000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>27</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>13.64</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>27</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>13.632999999999999</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>27</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>66.28</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>23</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>23</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>23</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>23</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>23</v>
       </c>
@@ -5904,7 +5904,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>23</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>23</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>23</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>23</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>23</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>23</v>
       </c>
@@ -6042,7 +6042,7 @@
         <v>70.52</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>23</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>28</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>28</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>12.78</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>28</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>28</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>28</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>28</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>28</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>28</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>28</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>28</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>28</v>
       </c>
@@ -6361,6 +6361,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K241" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="040414"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K241">
       <sortCondition ref="A1:A241"/>
     </sortState>
@@ -6425,6 +6430,12 @@
       <c r="D2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>25.323</v>
+      </c>
+      <c r="J2">
+        <v>12.68</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -6439,6 +6450,12 @@
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>24.94</v>
+      </c>
+      <c r="J3">
+        <v>12.816000000000001</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -6453,6 +6470,18 @@
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4">
+        <v>25.4</v>
+      </c>
+      <c r="F4">
+        <v>8.4060000000000006</v>
+      </c>
+      <c r="G4">
+        <v>14.25</v>
+      </c>
+      <c r="H4">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -6467,6 +6496,18 @@
       <c r="D5">
         <v>2</v>
       </c>
+      <c r="E5">
+        <v>25.4</v>
+      </c>
+      <c r="F5">
+        <v>9.82</v>
+      </c>
+      <c r="G5">
+        <v>14.25</v>
+      </c>
+      <c r="H5">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -6481,6 +6522,18 @@
       <c r="D6">
         <v>3</v>
       </c>
+      <c r="E6">
+        <v>25.4</v>
+      </c>
+      <c r="F6">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="G6">
+        <v>14.25</v>
+      </c>
+      <c r="H6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -6495,6 +6548,18 @@
       <c r="D7">
         <v>4</v>
       </c>
+      <c r="E7">
+        <v>25.4</v>
+      </c>
+      <c r="F7">
+        <v>8.4369999999999994</v>
+      </c>
+      <c r="G7">
+        <v>14.25</v>
+      </c>
+      <c r="H7">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -6509,6 +6574,18 @@
       <c r="D8">
         <v>1</v>
       </c>
+      <c r="E8">
+        <v>25.4</v>
+      </c>
+      <c r="F8">
+        <v>8.9130000000000003</v>
+      </c>
+      <c r="G8">
+        <v>14.25</v>
+      </c>
+      <c r="H8">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -6523,6 +6600,18 @@
       <c r="D9">
         <v>2</v>
       </c>
+      <c r="E9">
+        <v>25.4</v>
+      </c>
+      <c r="F9">
+        <v>8.0129999999999999</v>
+      </c>
+      <c r="G9">
+        <v>14.25</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -6537,6 +6626,18 @@
       <c r="D10">
         <v>3</v>
       </c>
+      <c r="E10">
+        <v>25.4</v>
+      </c>
+      <c r="F10">
+        <v>7.85</v>
+      </c>
+      <c r="G10">
+        <v>14.25</v>
+      </c>
+      <c r="H10">
+        <v>1.77</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -6551,6 +6652,18 @@
       <c r="D11">
         <v>4</v>
       </c>
+      <c r="E11">
+        <v>25.4</v>
+      </c>
+      <c r="F11">
+        <v>8.9559999999999995</v>
+      </c>
+      <c r="G11">
+        <v>14.25</v>
+      </c>
+      <c r="H11">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -6565,6 +6678,15 @@
       <c r="D12">
         <v>1</v>
       </c>
+      <c r="E12">
+        <v>12.82</v>
+      </c>
+      <c r="F12">
+        <v>5.86</v>
+      </c>
+      <c r="K12">
+        <v>68.5</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -6578,6 +6700,15 @@
       </c>
       <c r="D13">
         <v>1</v>
+      </c>
+      <c r="E13">
+        <v>12.86</v>
+      </c>
+      <c r="F13">
+        <v>5.76</v>
+      </c>
+      <c r="K13">
+        <v>71.400000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
+++ b/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2023_organized\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2023_organized\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161DD17-6581-49F3-B627-06A4CC600A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EA75DF-C119-4A51-8F73-1DB01E577C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15630" yWindow="2925" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="29">
   <si>
     <t>Section</t>
   </si>
@@ -485,14 +485,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K241"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>40316</v>
       </c>
@@ -547,7 +546,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>40316</v>
       </c>
@@ -567,7 +566,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>40316</v>
       </c>
@@ -593,7 +592,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>40316</v>
       </c>
@@ -619,7 +618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>40316</v>
       </c>
@@ -645,7 +644,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>40316</v>
       </c>
@@ -671,7 +670,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>40316</v>
       </c>
@@ -697,7 +696,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>40316</v>
       </c>
@@ -723,7 +722,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>40316</v>
       </c>
@@ -749,7 +748,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>40316</v>
       </c>
@@ -775,7 +774,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>40316</v>
       </c>
@@ -798,7 +797,7 @@
         <v>71.95</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>40316</v>
       </c>
@@ -821,7 +820,7 @@
         <v>59.76</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>40411</v>
       </c>
@@ -841,7 +840,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>40411</v>
       </c>
@@ -861,7 +860,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>40411</v>
       </c>
@@ -887,7 +886,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>40411</v>
       </c>
@@ -913,7 +912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>40411</v>
       </c>
@@ -939,7 +938,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>40411</v>
       </c>
@@ -965,7 +964,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>40411</v>
       </c>
@@ -991,7 +990,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>40411</v>
       </c>
@@ -1017,7 +1016,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>40411</v>
       </c>
@@ -1043,7 +1042,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>40411</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>40411</v>
       </c>
@@ -1092,7 +1091,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>40411</v>
       </c>
@@ -1115,7 +1114,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>40411</v>
       </c>
@@ -1135,7 +1134,7 @@
         <v>12.86</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>40411</v>
       </c>
@@ -1155,7 +1154,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>40411</v>
       </c>
@@ -1181,7 +1180,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>40411</v>
       </c>
@@ -1207,7 +1206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>40411</v>
       </c>
@@ -1233,7 +1232,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>40411</v>
       </c>
@@ -1259,7 +1258,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>40411</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>40411</v>
       </c>
@@ -1311,7 +1310,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>40411</v>
       </c>
@@ -1337,7 +1336,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>40411</v>
       </c>
@@ -1363,7 +1362,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>40411</v>
       </c>
@@ -1386,7 +1385,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>40411</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>40416</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>40416</v>
       </c>
@@ -1449,7 +1448,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>40416</v>
       </c>
@@ -1475,7 +1474,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40416</v>
       </c>
@@ -1501,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40416</v>
       </c>
@@ -1527,7 +1526,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>40416</v>
       </c>
@@ -1553,7 +1552,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>40416</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>40416</v>
       </c>
@@ -1605,7 +1604,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>40416</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>40416</v>
       </c>
@@ -1657,7 +1656,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>40416</v>
       </c>
@@ -1680,7 +1679,7 @@
         <v>70.34</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>40416</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>78.77</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>40417</v>
       </c>
@@ -1723,7 +1722,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>40417</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>12.305999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>40417</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>40417</v>
       </c>
@@ -1795,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>40417</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>40417</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>40417</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>40417</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>40417</v>
       </c>
@@ -1925,7 +1924,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>40417</v>
       </c>
@@ -1951,7 +1950,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>40417</v>
       </c>
@@ -1974,7 +1973,7 @@
         <v>68.7</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>40417</v>
       </c>
@@ -1997,7 +1996,7 @@
         <v>65.69</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>40508</v>
       </c>
@@ -2017,7 +2016,7 @@
         <v>12.68</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>40508</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>40508</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>40508</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>40508</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>40508</v>
       </c>
@@ -2141,7 +2140,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>40508</v>
       </c>
@@ -2167,7 +2166,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>40508</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>40508</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>40508</v>
       </c>
@@ -2245,7 +2244,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>40508</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>87.56</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>40508</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>90.42</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>40614</v>
       </c>
@@ -2311,7 +2310,7 @@
         <v>13.06</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>40614</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>12.95</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>40614</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>40614</v>
       </c>
@@ -2383,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>40614</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>40614</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>40614</v>
       </c>
@@ -2461,7 +2460,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>40614</v>
       </c>
@@ -2487,7 +2486,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>40614</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>40614</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>40614</v>
       </c>
@@ -2562,7 +2561,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>40614</v>
       </c>
@@ -2581,11 +2580,17 @@
       <c r="F85">
         <v>5.49</v>
       </c>
+      <c r="I85">
+        <v>23.56</v>
+      </c>
+      <c r="J85">
+        <v>12.99</v>
+      </c>
       <c r="K85">
         <v>72.27</v>
       </c>
     </row>
-    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>26</v>
       </c>
@@ -2598,17 +2603,17 @@
       <c r="D86">
         <v>1</v>
       </c>
-      <c r="E86">
-        <v>12.86</v>
-      </c>
-      <c r="F86">
-        <v>5.17</v>
+      <c r="I86">
+        <v>24.56</v>
+      </c>
+      <c r="J86">
+        <v>12.79</v>
       </c>
       <c r="K86">
         <v>81.11</v>
       </c>
     </row>
-    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>26</v>
       </c>
@@ -2621,17 +2626,11 @@
       <c r="D87">
         <v>1</v>
       </c>
-      <c r="E87">
-        <v>12.87</v>
-      </c>
-      <c r="F87">
-        <v>4.22</v>
-      </c>
       <c r="K87">
         <v>82.12</v>
       </c>
     </row>
-    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -2644,14 +2643,20 @@
       <c r="D88">
         <v>1</v>
       </c>
-      <c r="I88">
-        <v>23.56</v>
-      </c>
-      <c r="J88">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>25.4</v>
+      </c>
+      <c r="F88">
+        <v>7.01</v>
+      </c>
+      <c r="G88">
+        <v>14.25</v>
+      </c>
+      <c r="H88">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>26</v>
       </c>
@@ -2664,14 +2669,20 @@
       <c r="D89">
         <v>2</v>
       </c>
-      <c r="I89">
-        <v>24.56</v>
-      </c>
-      <c r="J89">
-        <v>12.79</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E89">
+        <v>25.4</v>
+      </c>
+      <c r="F89">
+        <v>7.69</v>
+      </c>
+      <c r="G89">
+        <v>14.25</v>
+      </c>
+      <c r="H89">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>26</v>
       </c>
@@ -2697,7 +2708,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>26</v>
       </c>
@@ -2723,7 +2734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -2749,7 +2760,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -2775,7 +2786,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -2801,7 +2812,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -2827,7 +2838,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -2841,19 +2852,13 @@
         <v>1</v>
       </c>
       <c r="E96">
-        <v>25.4</v>
+        <v>12.86</v>
       </c>
       <c r="F96">
-        <v>7.01</v>
-      </c>
-      <c r="G96">
-        <v>14.25</v>
-      </c>
-      <c r="H96">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -2867,19 +2872,13 @@
         <v>1</v>
       </c>
       <c r="E97">
-        <v>25.4</v>
+        <v>12.87</v>
       </c>
       <c r="F97">
-        <v>7.69</v>
-      </c>
-      <c r="G97">
-        <v>14.25</v>
-      </c>
-      <c r="H97">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2898,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2919,7 +2918,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -2945,7 +2944,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -2971,7 +2970,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -3023,7 +3022,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -3049,7 +3048,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -3075,7 +3074,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -3101,7 +3100,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -3127,7 +3126,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -3163,17 +3162,17 @@
       <c r="D109">
         <v>1</v>
       </c>
-      <c r="E109">
-        <v>12.86</v>
-      </c>
-      <c r="F109">
-        <v>3.67</v>
+      <c r="I109">
+        <v>23.56</v>
+      </c>
+      <c r="J109">
+        <v>12.99</v>
       </c>
       <c r="K109">
         <v>69.05</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -3186,17 +3185,17 @@
       <c r="D110">
         <v>1</v>
       </c>
-      <c r="E110">
-        <v>12.86</v>
-      </c>
-      <c r="F110">
-        <v>5.17</v>
+      <c r="I110">
+        <v>24.56</v>
+      </c>
+      <c r="J110">
+        <v>12.79</v>
       </c>
       <c r="K110">
         <v>81.11</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -3232,14 +3231,20 @@
       <c r="D112">
         <v>1</v>
       </c>
-      <c r="I112">
-        <v>23.56</v>
-      </c>
-      <c r="J112">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E112">
+        <v>25.4</v>
+      </c>
+      <c r="F112">
+        <v>7.01</v>
+      </c>
+      <c r="G112">
+        <v>14.25</v>
+      </c>
+      <c r="H112">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -3252,14 +3257,20 @@
       <c r="D113">
         <v>2</v>
       </c>
-      <c r="I113">
-        <v>24.56</v>
-      </c>
-      <c r="J113">
-        <v>12.79</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E113">
+        <v>25.4</v>
+      </c>
+      <c r="F113">
+        <v>7.69</v>
+      </c>
+      <c r="G113">
+        <v>14.25</v>
+      </c>
+      <c r="H113">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>25</v>
       </c>
@@ -3285,7 +3296,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>25</v>
       </c>
@@ -3311,7 +3322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -3337,7 +3348,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>25</v>
       </c>
@@ -3363,7 +3374,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>25</v>
       </c>
@@ -3389,7 +3400,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>25</v>
       </c>
@@ -3415,7 +3426,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>25</v>
       </c>
@@ -3429,19 +3440,13 @@
         <v>1</v>
       </c>
       <c r="E120">
-        <v>25.4</v>
+        <v>12.86</v>
       </c>
       <c r="F120">
-        <v>7.01</v>
-      </c>
-      <c r="G120">
-        <v>14.25</v>
-      </c>
-      <c r="H120">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>25</v>
       </c>
@@ -3455,19 +3460,13 @@
         <v>1</v>
       </c>
       <c r="E121">
-        <v>25.4</v>
+        <v>12.86</v>
       </c>
       <c r="F121">
-        <v>7.69</v>
-      </c>
-      <c r="G121">
-        <v>14.25</v>
-      </c>
-      <c r="H121">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -3487,7 +3486,7 @@
         <v>12.68</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -3507,7 +3506,7 @@
         <v>12.816000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -3715,7 +3714,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -3738,7 +3737,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -3784,7 +3783,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -3807,7 +3806,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -3827,7 +3826,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -3847,7 +3846,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -3899,7 +3898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -3925,7 +3924,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -3977,7 +3976,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -4003,7 +4002,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -4029,7 +4028,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -4055,7 +4054,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>81.11</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -4101,7 +4100,7 @@
         <v>82.12</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -4141,7 +4140,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -4193,7 +4192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -4219,7 +4218,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -4245,7 +4244,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -4271,7 +4270,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -4297,7 +4296,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -4323,7 +4322,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>20</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>20</v>
       </c>
@@ -4389,7 +4388,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>20</v>
       </c>
@@ -4415,7 +4414,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>20</v>
       </c>
@@ -4441,7 +4440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>20</v>
       </c>
@@ -4467,7 +4466,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>20</v>
       </c>
@@ -4493,7 +4492,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>20</v>
       </c>
@@ -4519,7 +4518,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>20</v>
       </c>
@@ -4545,7 +4544,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>20</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>20</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>20</v>
       </c>
@@ -4620,7 +4619,7 @@
         <v>90.42</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>20</v>
       </c>
@@ -4643,7 +4642,7 @@
         <v>87.56</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>21</v>
       </c>
@@ -4666,7 +4665,7 @@
         <v>59.26</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4688,7 @@
         <v>60.06</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>21</v>
       </c>
@@ -4712,7 +4711,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>21</v>
       </c>
@@ -4735,7 +4734,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>21</v>
       </c>
@@ -4758,7 +4757,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>21</v>
       </c>
@@ -4781,7 +4780,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>21</v>
       </c>
@@ -4804,7 +4803,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>21</v>
       </c>
@@ -4827,7 +4826,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>21</v>
       </c>
@@ -4850,7 +4849,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>21</v>
       </c>
@@ -4873,7 +4872,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>21</v>
       </c>
@@ -4893,7 +4892,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>21</v>
       </c>
@@ -4913,7 +4912,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>22</v>
       </c>
@@ -4933,7 +4932,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>22</v>
       </c>
@@ -4953,7 +4952,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>22</v>
       </c>
@@ -4979,7 +4978,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>22</v>
       </c>
@@ -5005,7 +5004,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -5031,7 +5030,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>22</v>
       </c>
@@ -5083,7 +5082,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>22</v>
       </c>
@@ -5109,7 +5108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -5135,7 +5134,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>22</v>
       </c>
@@ -5161,7 +5160,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>22</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>59.02</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>22</v>
       </c>
@@ -5207,7 +5206,7 @@
         <v>58.57</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>24</v>
       </c>
@@ -5227,7 +5226,7 @@
         <v>12.77</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>24</v>
       </c>
@@ -5247,7 +5246,7 @@
         <v>12.92</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>24</v>
       </c>
@@ -5273,7 +5272,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>24</v>
       </c>
@@ -5299,7 +5298,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>24</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>24</v>
       </c>
@@ -5351,7 +5350,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>24</v>
       </c>
@@ -5377,7 +5376,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>24</v>
       </c>
@@ -5403,7 +5402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>24</v>
       </c>
@@ -5429,7 +5428,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>24</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>24</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>61.88</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>24</v>
       </c>
@@ -5501,7 +5500,7 @@
         <v>63.08</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>27</v>
       </c>
@@ -5521,7 +5520,7 @@
         <v>24.45</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>27</v>
       </c>
@@ -5541,7 +5540,7 @@
         <v>23.22</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>27</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>13.65</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>27</v>
       </c>
@@ -5593,7 +5592,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>27</v>
       </c>
@@ -5619,7 +5618,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>27</v>
       </c>
@@ -5645,7 +5644,7 @@
         <v>13.557</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>27</v>
       </c>
@@ -5671,7 +5670,7 @@
         <v>13.87</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>27</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>13.563000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>27</v>
       </c>
@@ -5723,7 +5722,7 @@
         <v>13.64</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>27</v>
       </c>
@@ -5749,7 +5748,7 @@
         <v>13.632999999999999</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>27</v>
       </c>
@@ -5772,7 +5771,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>27</v>
       </c>
@@ -5795,7 +5794,7 @@
         <v>66.28</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>23</v>
       </c>
@@ -5815,7 +5814,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>23</v>
       </c>
@@ -5835,7 +5834,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>23</v>
       </c>
@@ -5858,7 +5857,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>23</v>
       </c>
@@ -5881,7 +5880,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>23</v>
       </c>
@@ -5904,7 +5903,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>23</v>
       </c>
@@ -5927,7 +5926,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>23</v>
       </c>
@@ -5950,7 +5949,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>23</v>
       </c>
@@ -5973,7 +5972,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>23</v>
       </c>
@@ -5996,7 +5995,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>23</v>
       </c>
@@ -6019,7 +6018,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>23</v>
       </c>
@@ -6042,7 +6041,7 @@
         <v>70.52</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>23</v>
       </c>
@@ -6065,7 +6064,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>28</v>
       </c>
@@ -6085,7 +6084,7 @@
         <v>12.88</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>28</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>12.78</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>28</v>
       </c>
@@ -6131,7 +6130,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>28</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>28</v>
       </c>
@@ -6183,7 +6182,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>28</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>28</v>
       </c>
@@ -6235,7 +6234,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>28</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -6287,7 +6286,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>28</v>
       </c>
@@ -6313,9 +6312,9 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
-        <v>28</v>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>42115</v>
       </c>
       <c r="B240" t="s">
         <v>12</v>
@@ -6336,7 +6335,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>28</v>
       </c>
@@ -6361,11 +6360,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K241" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="040414"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K241">
       <sortCondition ref="A1:A241"/>
     </sortState>
@@ -6377,12 +6371,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6417,7 +6411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>111518</v>
       </c>
@@ -6437,7 +6431,7 @@
         <v>12.68</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>111518</v>
       </c>
@@ -6457,7 +6451,7 @@
         <v>12.816000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>111518</v>
       </c>
@@ -6483,7 +6477,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>111518</v>
       </c>
@@ -6509,7 +6503,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>111518</v>
       </c>
@@ -6535,7 +6529,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>111518</v>
       </c>
@@ -6561,7 +6555,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>111518</v>
       </c>
@@ -6587,7 +6581,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>111518</v>
       </c>
@@ -6613,7 +6607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>111518</v>
       </c>
@@ -6639,7 +6633,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>111518</v>
       </c>
@@ -6665,7 +6659,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>111518</v>
       </c>
@@ -6688,7 +6682,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>111518</v>
       </c>

--- a/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
+++ b/OrganizedData/2023_organized/SpecimenDimensions2023.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EA75DF-C119-4A51-8F73-1DB01E577C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
